--- a/data/trans_bre/IP2003-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 16,61</t>
+          <t>-2,02; 16,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 12,53</t>
+          <t>-8,33; 10,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 0,95</t>
+          <t>-19,22; -0,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 27,82</t>
+          <t>-4,08; 25,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 162,72</t>
+          <t>-11,28; 149,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,73; 84,49</t>
+          <t>-34,93; 70,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-81,9; 15,38</t>
+          <t>-81,64; 8,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-46,86; 1466,46</t>
+          <t>-58,75; 901,08</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,12</t>
+          <t>1,07; 9,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 6,8</t>
+          <t>-1,33; 6,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 6,29</t>
+          <t>-1,42; 5,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 20,01</t>
+          <t>-4,47; 17,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 72,99</t>
+          <t>6,22; 72,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 53,99</t>
+          <t>-8,69; 54,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 57,13</t>
+          <t>-10,03; 53,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,38; 150,88</t>
+          <t>-26,73; 144,98</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 2,66</t>
+          <t>-9,15; 3,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 13,36</t>
+          <t>1,52; 13,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 6,25</t>
+          <t>-5,68; 6,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 9,02</t>
+          <t>-4,19; 9,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-54,82; 29,52</t>
+          <t>-55,49; 34,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,31; 260,83</t>
+          <t>13,72; 282,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-43,74; 81,08</t>
+          <t>-43,82; 73,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,69; 98,89</t>
+          <t>-28,96; 103,64</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 6,34</t>
+          <t>0,15; 6,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,7</t>
+          <t>0,51; 6,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,36</t>
+          <t>-2,21; 3,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 16,11</t>
+          <t>-2,81; 14,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 49,0</t>
+          <t>0,54; 50,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,73; 57,11</t>
+          <t>3,43; 55,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 28,76</t>
+          <t>-15,59; 31,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 128,66</t>
+          <t>-18,42; 110,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2003-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 16,73</t>
+          <t>-2,76; 16,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 10,68</t>
+          <t>-8,42; 11,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,22; -0,08</t>
+          <t>-19,64; -0,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 25,67</t>
+          <t>-4,27; 25,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 149,48</t>
+          <t>-14,67; 155,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 70,13</t>
+          <t>-34,56; 81,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-81,64; 8,63</t>
+          <t>-81,25; 2,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-58,75; 901,08</t>
+          <t>-55,3; 702,07</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,32</t>
+          <t>1,1; 9,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 6,73</t>
+          <t>-1,39; 6,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 5,96</t>
+          <t>-1,97; 5,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 17,45</t>
+          <t>-4,95; 16,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,22; 72,35</t>
+          <t>6,15; 77,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 54,33</t>
+          <t>-9,33; 53,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 53,58</t>
+          <t>-12,96; 54,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 144,98</t>
+          <t>-29,67; 125,58</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 3,15</t>
+          <t>-8,66; 2,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 13,68</t>
+          <t>2,26; 13,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 6,12</t>
+          <t>-6,36; 4,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 9,2</t>
+          <t>-4,17; 8,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,49; 34,88</t>
+          <t>-53,53; 31,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,72; 282,31</t>
+          <t>17,47; 276,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-43,82; 73,99</t>
+          <t>-45,42; 58,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,96; 103,64</t>
+          <t>-27,65; 100,7</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 6,59</t>
+          <t>0,15; 6,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,46</t>
+          <t>0,62; 6,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,65</t>
+          <t>-2,56; 3,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 14,28</t>
+          <t>-2,36; 14,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 50,15</t>
+          <t>0,43; 53,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 55,69</t>
+          <t>4,14; 57,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 31,91</t>
+          <t>-18,02; 33,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 110,19</t>
+          <t>-16,9; 117,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2003-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,39</t>
+          <t>3,47</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 16,4</t>
+          <t>-2,46; 16,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 11,11</t>
+          <t>-8,67; 12,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,64; -0,14</t>
+          <t>-19,45; 0,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 25,53</t>
+          <t>-4,56; 14,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 155,72</t>
+          <t>-14,52; 162,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,56; 81,0</t>
+          <t>-35,73; 84,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-81,25; 2,4</t>
+          <t>-81,9; 15,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-55,3; 702,07</t>
+          <t>-52,85; 662,18</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,88</t>
+          <t>-1,07</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>-7,0%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 9,64</t>
+          <t>0,93; 9,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 6,58</t>
+          <t>-1,5; 6,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 5,91</t>
+          <t>-1,86; 6,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 16,82</t>
+          <t>-7,12; 4,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 77,43</t>
+          <t>5,57; 72,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 53,87</t>
+          <t>-9,9; 53,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 54,75</t>
+          <t>-13,3; 57,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,67; 125,58</t>
+          <t>-36,19; 33,29</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>3,2</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 2,97</t>
+          <t>-9,04; 2,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 13,87</t>
+          <t>1,4; 13,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 4,85</t>
+          <t>-6,0; 6,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 8,84</t>
+          <t>-4,09; 9,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,53; 31,39</t>
+          <t>-54,82; 29,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,47; 276,84</t>
+          <t>8,31; 260,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-45,42; 58,42</t>
+          <t>-43,74; 81,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 100,7</t>
+          <t>-28,61; 107,21</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,17</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 6,89</t>
+          <t>-0,02; 6,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,96</t>
+          <t>0,49; 6,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 3,77</t>
+          <t>-2,84; 3,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 14,68</t>
+          <t>-4,15; 4,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 53,28</t>
+          <t>-0,23; 49,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 57,92</t>
+          <t>3,73; 57,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 33,27</t>
+          <t>-18,73; 28,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 117,97</t>
+          <t>-25,35; 36,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2003-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>6,76</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-9,65</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,47</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>43,06%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-51,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>52,38%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>6.763249712892389</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.217681681340718</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-9.646682951363198</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.474038976600893</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.4305720951059969</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.06307722427718883</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.5177653676191686</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.523755240668878</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-2,46; 16,61</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-8,67; 12,53</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-19,45; 0,95</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-4,56; 14,36</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-14,52; 162,72</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-35,73; 84,49</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-81,9; 15,38</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-52,85; 662,18</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.457170683069</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-8.670220474849719</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-19.44824657211644</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-4.558701589746653</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.145239560968766</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.357255309784591</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.8189612369350577</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.5284981937172408</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>16.61034752570288</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.53266797651534</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9489767942186147</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>14.35552484290055</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.627243378574029</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.8449120614440423</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.1537599448106817</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>6.6217689579441</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5,17</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,55</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,16</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,07</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>36,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,04%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-7,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,93; 9,12</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,5; 6,8</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,86; 6,29</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-7,12; 4,08</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,57; 72,99</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-9,9; 53,99</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-13,3; 57,13</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-36,19; 33,29</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>5.168573702870255</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.545698915731509</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.159232363174757</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.073083503012695</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.3603756626156162</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1803581722698383</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.1680362718804668</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.06995037864316374</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,99</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7,7</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-22,68%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>105,95%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-0,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>27,23%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.9259080698186083</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.501329172153436</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.861738380938458</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-7.115813445020628</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.05572742752661313</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.09903849618822072</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.133032604472665</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3618781736530163</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-9,04; 2,66</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,4; 13,36</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,0; 6,25</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-4,09; 9,5</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-54,82; 29,52</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>8,31; 260,83</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-43,74; 81,08</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-28,61; 107,21</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>9.123713359119032</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6.795304683865905</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.292470293148171</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.078611308266523</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.7299313358360995</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.5399330735273586</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.5713294425335946</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.3328739045832062</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3,58</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,21%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,08%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.987829492117839</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>7.696192632435446</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.05221854064204473</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3.195438494380054</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2268472978829829</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1.059512112301421</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.004726379444640888</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.2722571899848304</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,02; 6,34</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,49; 6,7</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,84; 3,36</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,15; 4,09</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-0,23; 49,0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3,73; 57,11</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-18,73; 28,76</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-25,35; 36,09</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.035187408898464</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.398592987299701</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.000435395618227</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.087446583435417</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.548217501717512</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>0.08307029578332051</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4374263946984643</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2860772159068979</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.659368063188784</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>13.35939155488359</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.248679378627967</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>9.50006870239182</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.2952343424696369</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>2.608308480257875</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.8107757245885377</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.072110222660093</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>3.309508026788619</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3.575713278460363</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.5383522527819762</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.3473277060135532</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.2321467519680908</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.2708061230624246</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.04150978807649428</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.02522121560292191</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.02289881045251646</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4946870991241671</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.838543395074778</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.151994976449477</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.00228239915087439</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.03726432654622949</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1872563844705683</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.2535354783720096</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.343281178543638</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.698297873181117</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.363627043481517</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.091189836233201</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.490009792347874</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.5711036733846911</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.287550788088451</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.3609032028709708</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
